--- a/Documentation/faraway_data.xlsx
+++ b/Documentation/faraway_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\FLo\GitHub\Faraway-Project\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\FLo\GitHub\Faraway-Project - Copie\Faraway\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F641709-A924-427F-B874-5DF718F13FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E428638-1662-415B-8512-CA03512C77F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3165" windowWidth="29040" windowHeight="15840" xr2:uid="{5807B1E4-6C51-4FFE-9D65-BF47CB68D2BB}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="87">
   <si>
     <t>condition</t>
   </si>
@@ -103,33 +103,6 @@
     <t>mana,map</t>
   </si>
   <si>
-    <t>antilope,mana</t>
-  </si>
-  <si>
-    <t>mana,mana</t>
-  </si>
-  <si>
-    <t>pineapple,mana</t>
-  </si>
-  <si>
-    <t>map,mana</t>
-  </si>
-  <si>
-    <t>antilope,pineapple</t>
-  </si>
-  <si>
-    <t>map,antilope</t>
-  </si>
-  <si>
-    <t>map,pineapple</t>
-  </si>
-  <si>
-    <t>mana,antilope</t>
-  </si>
-  <si>
-    <t>mana,pineapple</t>
-  </si>
-  <si>
     <t>g,y</t>
   </si>
   <si>
@@ -145,66 +118,6 @@
     <t>b,y</t>
   </si>
   <si>
-    <t>antilope,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,mana</t>
-  </si>
-  <si>
-    <t>pineapple,antilope,mana</t>
-  </si>
-  <si>
-    <t>antilope,mana,mana</t>
-  </si>
-  <si>
-    <t>antilope,antilope,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,antilope</t>
-  </si>
-  <si>
-    <t>pineapple,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,pineapple</t>
-  </si>
-  <si>
-    <t>pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>mana,mana,mana,mana</t>
-  </si>
-  <si>
-    <t>antilope,pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>antilope,antilope,mana</t>
-  </si>
-  <si>
-    <t>pineapple,pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>antilope,antilope,antilope,mana</t>
-  </si>
-  <si>
-    <t>mana,mana,antilope,antilope</t>
-  </si>
-  <si>
-    <t>antilope,antilope,antilope,antilope</t>
-  </si>
-  <si>
-    <t>pineapple,pineapple, pineapple</t>
-  </si>
-  <si>
-    <t>pineapple,antilope,antilope</t>
-  </si>
-  <si>
-    <t>mana,mana,pineapple,pineapple</t>
-  </si>
-  <si>
-    <t>antilope,antilope,pineapple,pineapple</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -223,9 +136,6 @@
     <t>activation_requirements</t>
   </si>
   <si>
-    <t>conditional_effect</t>
-  </si>
-  <si>
     <t>g,r</t>
   </si>
   <si>
@@ -244,29 +154,158 @@
     <t>map,night</t>
   </si>
   <si>
-    <t>mana,antilope,night</t>
-  </si>
-  <si>
-    <t>mana,pineapple,night</t>
-  </si>
-  <si>
     <t>4colors</t>
   </si>
   <si>
-    <t>mana,mana,mana,mana,mana</t>
+    <t>map,thistle</t>
+  </si>
+  <si>
+    <t>thistle</t>
+  </si>
+  <si>
+    <t>thistle,night</t>
+  </si>
+  <si>
+    <t>thistle,thistle</t>
+  </si>
+  <si>
+    <t>thistle,thistle,thistle</t>
+  </si>
+  <si>
+    <t>thistle,thistle, thistle</t>
+  </si>
+  <si>
+    <t>thistle,map</t>
+  </si>
+  <si>
+    <t>stone,stone</t>
+  </si>
+  <si>
+    <t>thistle,stone</t>
+  </si>
+  <si>
+    <t>map,stone</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>stone,night</t>
+  </si>
+  <si>
+    <t>stone,stone,stone</t>
+  </si>
+  <si>
+    <t>stone,thistle,night</t>
+  </si>
+  <si>
+    <t>stone,thistle</t>
+  </si>
+  <si>
+    <t>stone,stone,thistle</t>
+  </si>
+  <si>
+    <t>stone,stone,stone,stone</t>
+  </si>
+  <si>
+    <t>stone,map</t>
+  </si>
+  <si>
+    <t>stone,stone,thistle,thistle</t>
+  </si>
+  <si>
+    <t>stone,stone,stone,stone,stone</t>
+  </si>
+  <si>
+    <t>chimera,stone</t>
+  </si>
+  <si>
+    <t>chimera</t>
+  </si>
+  <si>
+    <t>chimera,thistle</t>
+  </si>
+  <si>
+    <t>map,chimera</t>
+  </si>
+  <si>
+    <t>chimera,chimera</t>
+  </si>
+  <si>
+    <t>stone,chimera,night</t>
+  </si>
+  <si>
+    <t>chimera,night</t>
+  </si>
+  <si>
+    <t>thistle,chimera,stone</t>
+  </si>
+  <si>
+    <t>chimera,stone,stone</t>
+  </si>
+  <si>
+    <t>stone,chimera</t>
+  </si>
+  <si>
+    <t>chimera,chimera,chimera</t>
+  </si>
+  <si>
+    <t>stone,stone,chimera</t>
+  </si>
+  <si>
+    <t>thistle,chimera</t>
+  </si>
+  <si>
+    <t>chimera,thistle,thistle</t>
+  </si>
+  <si>
+    <t>chimera,chimera,stone</t>
+  </si>
+  <si>
+    <t>chimera,chimera,chimera,stone</t>
+  </si>
+  <si>
+    <t>stone,stone,chimera,chimera</t>
+  </si>
+  <si>
+    <t>chimera,chimera,chimera,chimera</t>
+  </si>
+  <si>
+    <t>thistle,chimera,chimera</t>
+  </si>
+  <si>
+    <t>chimera,chimera,thistle,thistle</t>
+  </si>
+  <si>
+    <t>chimera,map</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>multiplicator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -289,8 +328,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,8 +647,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE3A926-3F08-4605-9E64-59CA287C1814}">
-  <dimension ref="A1:G114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H114"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="33.140625" customWidth="1"/>
@@ -614,18 +656,18 @@
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -634,41 +676,44 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="E4">
         <v>4</v>
       </c>
@@ -676,29 +721,29 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -707,55 +752,58 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="E10">
         <v>5</v>
       </c>
@@ -763,13 +811,19 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
       <c r="E11">
         <v>3</v>
       </c>
@@ -777,13 +831,16 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
@@ -794,15 +851,15 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -811,15 +868,18 @@
         <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -828,15 +888,15 @@
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -848,10 +908,10 @@
         <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -859,7 +919,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -868,18 +928,21 @@
         <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -888,21 +951,21 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -911,18 +974,18 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -931,18 +994,18 @@
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -951,18 +1014,18 @@
         <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -974,10 +1037,10 @@
         <v>3</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -985,7 +1048,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -994,15 +1057,15 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -1014,18 +1077,18 @@
         <v>3</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -1034,18 +1097,21 @@
         <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -1057,10 +1123,10 @@
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1068,7 +1134,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1077,18 +1143,18 @@
         <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -1097,10 +1163,13 @@
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="H27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1108,7 +1177,7 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1117,18 +1186,18 @@
         <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1137,18 +1206,18 @@
         <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -1157,18 +1226,18 @@
         <v>6</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -1177,10 +1246,10 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1188,7 +1257,7 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -1197,18 +1266,18 @@
         <v>6</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -1217,18 +1286,18 @@
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -1237,21 +1306,21 @@
         <v>6</v>
       </c>
       <c r="G34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -1260,18 +1329,18 @@
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -1280,10 +1349,10 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1291,10 +1360,10 @@
         <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -1303,10 +1372,10 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1314,7 +1383,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -1326,18 +1395,18 @@
         <v>6</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
@@ -1349,18 +1418,18 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E40">
         <v>9</v>
@@ -1369,10 +1438,10 @@
         <v>4</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1380,7 +1449,7 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -1392,18 +1461,18 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -1415,18 +1484,21 @@
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>42</v>
       </c>
+      <c r="B43" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -1435,18 +1507,18 @@
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E44">
         <v>10</v>
@@ -1455,18 +1527,21 @@
         <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>44</v>
       </c>
+      <c r="B45" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -1475,18 +1550,18 @@
         <v>6</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E46">
         <v>13</v>
@@ -1495,10 +1570,10 @@
         <v>3</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1506,7 +1581,7 @@
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E47">
         <v>10</v>
@@ -1515,18 +1590,21 @@
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>47</v>
       </c>
+      <c r="B48" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E48">
         <v>2</v>
@@ -1535,18 +1613,18 @@
         <v>6</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -1555,10 +1633,13 @@
         <v>4</v>
       </c>
       <c r="G49" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1566,7 +1647,7 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E50">
         <v>12</v>
@@ -1575,18 +1656,18 @@
         <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
         <v>3</v>
@@ -1598,18 +1679,18 @@
         <v>6</v>
       </c>
       <c r="G51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>14</v>
@@ -1618,18 +1699,21 @@
         <v>5</v>
       </c>
       <c r="G52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>52</v>
       </c>
+      <c r="B53" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -1638,18 +1722,18 @@
         <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
         <v>4</v>
@@ -1661,18 +1745,18 @@
         <v>6</v>
       </c>
       <c r="G54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D55" t="s">
         <v>14</v>
@@ -1684,21 +1768,21 @@
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -1707,18 +1791,18 @@
         <v>5</v>
       </c>
       <c r="G56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
@@ -1730,18 +1814,21 @@
         <v>6</v>
       </c>
       <c r="G57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>57</v>
       </c>
+      <c r="B58" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E58">
         <v>4</v>
@@ -1750,10 +1837,10 @@
         <v>4</v>
       </c>
       <c r="G58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1761,7 +1848,7 @@
         <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
@@ -1773,10 +1860,10 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1784,10 +1871,10 @@
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -1796,10 +1883,10 @@
         <v>6</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1807,7 +1894,7 @@
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E61">
         <v>16</v>
@@ -1816,18 +1903,18 @@
         <v>5</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E62">
         <v>17</v>
@@ -1836,10 +1923,10 @@
         <v>3</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1847,10 +1934,10 @@
         <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -1859,10 +1946,10 @@
         <v>6</v>
       </c>
       <c r="G63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1870,7 +1957,7 @@
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="E64">
         <v>15</v>
@@ -1879,10 +1966,10 @@
         <v>3</v>
       </c>
       <c r="G64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1890,7 +1977,7 @@
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>18</v>
@@ -1899,10 +1986,10 @@
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1910,10 +1997,10 @@
         <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -1922,15 +2009,18 @@
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>66</v>
       </c>
+      <c r="B67" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E67">
         <v>20</v>
@@ -1939,10 +2029,10 @@
         <v>5</v>
       </c>
       <c r="G67" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1950,7 +2040,7 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E68">
         <v>19</v>
@@ -1959,15 +2049,18 @@
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>68</v>
       </c>
+      <c r="B69" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E69">
         <v>24</v>
@@ -1976,13 +2069,14 @@
         <v>5</v>
       </c>
       <c r="G69" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>69</v>
       </c>
+      <c r="B70" s="1"/>
       <c r="D70" t="s">
         <v>3</v>
       </c>
@@ -1993,13 +2087,14 @@
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>70</v>
       </c>
+      <c r="B71" s="1"/>
       <c r="D71" t="s">
         <v>4</v>
       </c>
@@ -2010,13 +2105,14 @@
         <v>4</v>
       </c>
       <c r="G71" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>71</v>
       </c>
+      <c r="B72" s="1"/>
       <c r="D72" t="s">
         <v>5</v>
       </c>
@@ -2027,13 +2123,14 @@
         <v>5</v>
       </c>
       <c r="G72" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>72</v>
       </c>
+      <c r="B73" s="1"/>
       <c r="D73" t="s">
         <v>6</v>
       </c>
@@ -2044,164 +2141,170 @@
         <v>6</v>
       </c>
       <c r="G73" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>73</v>
       </c>
+      <c r="B74" s="1"/>
       <c r="D74" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>74</v>
       </c>
+      <c r="B75" s="1"/>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>75</v>
       </c>
+      <c r="B76" s="1"/>
       <c r="D76" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>76</v>
       </c>
+      <c r="B77" s="1"/>
       <c r="D77" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>77</v>
       </c>
+      <c r="B78" s="1"/>
       <c r="D78" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>78</v>
       </c>
+      <c r="B79" s="1"/>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F80" t="s">
         <v>5</v>
       </c>
       <c r="G80" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F81" t="s">
         <v>5</v>
       </c>
       <c r="G81" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F82" t="s">
         <v>5</v>
       </c>
       <c r="G82" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F83" t="s">
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F84" t="s">
         <v>3</v>
       </c>
       <c r="G84" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2212,66 +2315,66 @@
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F86" t="s">
         <v>4</v>
       </c>
       <c r="G86" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F87" t="s">
         <v>4</v>
       </c>
       <c r="G87" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F88" t="s">
         <v>4</v>
       </c>
       <c r="G88" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
       </c>
       <c r="G89" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2282,15 +2385,16 @@
         <v>6</v>
       </c>
       <c r="G90" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>90</v>
       </c>
+      <c r="B91" s="1"/>
       <c r="D91" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E91">
         <v>4</v>
@@ -2299,13 +2403,14 @@
         <v>6</v>
       </c>
       <c r="G91" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>91</v>
       </c>
+      <c r="B92" s="1"/>
       <c r="D92" t="s">
         <v>14</v>
       </c>
@@ -2316,21 +2421,22 @@
         <v>6</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>92</v>
       </c>
+      <c r="B93" s="1"/>
       <c r="E93">
         <v>5</v>
       </c>
       <c r="G93" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2341,85 +2447,88 @@
         <v>5</v>
       </c>
       <c r="G94" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G95" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="G96" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98">
         <v>97</v>
       </c>
+      <c r="B98" s="1"/>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E98">
         <v>2</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99">
         <v>98</v>
       </c>
+      <c r="B99" s="1"/>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E99">
         <v>2</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100">
         <v>99</v>
       </c>
+      <c r="B100" s="1"/>
       <c r="D100" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="G100" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2430,10 +2539,10 @@
         <v>2</v>
       </c>
       <c r="G101" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2441,16 +2550,16 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E102">
         <v>4</v>
       </c>
       <c r="G102" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2464,15 +2573,15 @@
         <v>3</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
@@ -2481,15 +2590,15 @@
         <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D105" t="s">
         <v>14</v>
@@ -2498,15 +2607,15 @@
         <v>1</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D106" t="s">
         <v>14</v>
@@ -2515,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>106</v>
       </c>
@@ -2532,61 +2641,61 @@
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E108">
         <v>1</v>
       </c>
       <c r="G108" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="D109" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E109">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111">
         <v>110</v>
       </c>
@@ -2597,40 +2706,40 @@
         <v>4</v>
       </c>
       <c r="G111" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="G112" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="G113" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="G114" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2641,14 +2750,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED7A518-DA0F-4443-8E3B-A0086BF59CED}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -2660,10 +2769,10 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>101</v>
       </c>
@@ -2677,7 +2786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>102</v>
       </c>
@@ -2691,7 +2800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>103</v>
       </c>
@@ -2705,7 +2814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>104</v>
       </c>
@@ -2719,7 +2828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>105</v>
       </c>
@@ -2730,7 +2839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>106</v>
       </c>
@@ -2741,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>107</v>
       </c>
@@ -2752,7 +2861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>108</v>
       </c>
@@ -2763,7 +2872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>109</v>
       </c>
@@ -2774,7 +2883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>110</v>
       </c>
@@ -2785,7 +2894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>111</v>
       </c>
@@ -2796,7 +2905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>112</v>
       </c>
@@ -2807,7 +2916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>113</v>
       </c>
@@ -2818,7 +2927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>114</v>
       </c>
@@ -2829,7 +2938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>115</v>
       </c>
@@ -2840,7 +2949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>116</v>
       </c>
@@ -2851,7 +2960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>117</v>
       </c>
@@ -2862,7 +2971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>118</v>
       </c>
@@ -2873,7 +2982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>119</v>
       </c>
@@ -2884,7 +2993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>120</v>
       </c>
@@ -2895,7 +3004,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>121</v>
       </c>
@@ -2906,7 +3015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>122</v>
       </c>
@@ -2920,7 +3029,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>123</v>
       </c>
@@ -2934,7 +3043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>124</v>
       </c>
@@ -2942,7 +3051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>125</v>
       </c>
@@ -2953,7 +3062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>126</v>
       </c>
@@ -2961,7 +3070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>127</v>
       </c>
@@ -2969,7 +3078,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>128</v>
       </c>
@@ -2977,7 +3086,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>129</v>
       </c>
@@ -2988,7 +3097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>130</v>
       </c>
@@ -2999,7 +3108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>131</v>
       </c>
@@ -3010,7 +3119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>132</v>
       </c>
@@ -3021,7 +3130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>133</v>
       </c>
@@ -3035,7 +3144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>134</v>
       </c>
@@ -3049,7 +3158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>135</v>
       </c>
@@ -3063,7 +3172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>136</v>
       </c>
@@ -3077,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>137</v>
       </c>
@@ -3091,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>138</v>
       </c>
@@ -3105,7 +3214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>139</v>
       </c>
@@ -3119,7 +3228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>140</v>
       </c>
@@ -3133,7 +3242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>141</v>
       </c>
@@ -3147,7 +3256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>142</v>
       </c>
@@ -3158,7 +3267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>143</v>
       </c>
@@ -3166,7 +3275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>144</v>
       </c>
@@ -3174,7 +3283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>145</v>
       </c>
